--- a/templates/data_curator/Config/data_curator_parameters.xlsx
+++ b/templates/data_curator/Config/data_curator_parameters.xlsx
@@ -1719,13 +1719,13 @@
   <phoneticPr fontId="16"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B5" xr:uid="{2E694D9E-5091-4438-84ED-E24E52EF7C10}">
-      <formula1>"FinancialModelingPrep,LsegWorkspace,YahooFinance,None"</formula1>
+      <formula1>"FinancialModelingPrep,LsegWorkspace,Sharadar,YahooFinance,None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{24DE7AE5-DCAA-4E1E-AB0A-0B7231D19E90}">
-      <formula1>"FinancialModelingPrep,LsegWorkspace,YahooFinance"</formula1>
+      <formula1>"FinancialModelingPrep,LsegWorkspace,Sharadar,YahooFinance"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{6764D2B7-BDEA-47DC-8E6C-55F0307CCA1A}">
-      <formula1>"FinancialModelingPrep,LsegWorkspace,None"</formula1>
+      <formula1>"FinancialModelingPrep,LsegWorkspace,Sharadar,None"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/data_curator/Config/data_curator_parameters.xlsx
+++ b/templates/data_curator/Config/data_curator_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rinku\Current Projects\KaxaNuk\Data-Curator\templates\data_curator\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0E8E9F-6BF4-42FD-87D8-5528E904D526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EF6DC7-403D-40BA-93C6-1F178FCD80C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="15810" windowWidth="19980" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29490" yWindow="14325" windowWidth="19980" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -738,10 +738,6 @@
   </si>
   <si>
     <t>fcf_net_cash_from_investing_activities</t>
-  </si>
-  <si>
-    <t>0.50.0</t>
-    <phoneticPr fontId="16"/>
   </si>
   <si>
     <t>data_block</t>
@@ -839,6 +835,10 @@
       </rPr>
       <t xml:space="preserve"> if you don’t need split data or there’s none available.</t>
     </r>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>0.51.0</t>
     <phoneticPr fontId="16"/>
   </si>
 </sst>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>16</v>
@@ -1617,59 +1617,59 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>226</v>
-      </c>
       <c r="C1" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
       <c r="A3" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B3" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="D3" s="28"/>
     </row>
     <row r="4" spans="1:4" ht="30">
       <c r="A4" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D4" s="28"/>
     </row>
     <row r="5" spans="1:4" ht="30">
       <c r="A5" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>233</v>
-      </c>
       <c r="C5" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D5" s="28"/>
     </row>
